--- a/research/traditional_assets/database/data/canada/canada_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_furn_home_furnishings.xlsx
@@ -588,37 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.08160000000000001</v>
-      </c>
-      <c r="E2">
-        <v>0.412</v>
+        <v>-0.12</v>
       </c>
       <c r="G2">
-        <v>0.04113372965831982</v>
+        <v>-0.02865849234564319</v>
       </c>
       <c r="H2">
-        <v>0.02600132108328829</v>
+        <v>-0.04781252267285788</v>
       </c>
       <c r="I2">
-        <v>-0.03554915030324866</v>
+        <v>-0.06087208880504971</v>
       </c>
       <c r="J2">
-        <v>-0.03554915030324866</v>
+        <v>-0.06087208880504971</v>
       </c>
       <c r="K2">
-        <v>157.3</v>
+        <v>-99.5</v>
       </c>
       <c r="L2">
-        <v>0.09445745511319283</v>
+        <v>-0.07219037945294929</v>
       </c>
       <c r="M2">
-        <v>0.499</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.004004815409309792</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.003172282263191354</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,82 +624,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.499</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>23</v>
+        <v>24.6</v>
       </c>
       <c r="V2">
-        <v>0.1845906902086678</v>
+        <v>0.1589147286821705</v>
       </c>
       <c r="W2">
-        <v>0.3197154471544716</v>
+        <v>-0.3055896805896806</v>
       </c>
       <c r="X2">
-        <v>0.2683463109506102</v>
+        <v>0.1616288447441349</v>
       </c>
       <c r="Y2">
-        <v>0.05136913620386135</v>
+        <v>-0.4672185253338154</v>
       </c>
       <c r="Z2">
-        <v>1.735229759299781</v>
+        <v>2.019783118405627</v>
       </c>
       <c r="AA2">
-        <v>-0.06168594352401792</v>
+        <v>-0.1229484173505276</v>
       </c>
       <c r="AB2">
-        <v>0.1261211761872993</v>
+        <v>0.07401100354284262</v>
       </c>
       <c r="AC2">
-        <v>-0.1878071197113172</v>
+        <v>-0.1969594208933702</v>
       </c>
       <c r="AD2">
-        <v>424.5</v>
+        <v>391.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>424.5</v>
+        <v>391.2</v>
       </c>
       <c r="AG2">
-        <v>401.5</v>
+        <v>366.6</v>
       </c>
       <c r="AH2">
-        <v>0.7730832270988891</v>
+        <v>0.7164835164835165</v>
       </c>
       <c r="AI2">
-        <v>0.5659245433942141</v>
+        <v>0.6342412451361868</v>
       </c>
       <c r="AJ2">
-        <v>0.7631628967876829</v>
+        <v>0.7031070195627157</v>
       </c>
       <c r="AK2">
-        <v>0.5521936459909228</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="AL2">
-        <v>23.9</v>
+        <v>25.5</v>
       </c>
       <c r="AM2">
-        <v>23.9</v>
+        <v>25.5</v>
       </c>
       <c r="AN2">
-        <v>-11.53532608695652</v>
+        <v>-6.596964586846543</v>
       </c>
       <c r="AO2">
-        <v>-2.476987447698745</v>
+        <v>-3.290196078431373</v>
       </c>
       <c r="AP2">
-        <v>-10.91032608695652</v>
+        <v>-6.182124789207419</v>
       </c>
       <c r="AQ2">
-        <v>-2.476987447698745</v>
+        <v>-3.290196078431373</v>
       </c>
     </row>
     <row r="3">
@@ -722,37 +716,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.08160000000000001</v>
-      </c>
-      <c r="E3">
-        <v>0.412</v>
+        <v>-0.12</v>
       </c>
       <c r="G3">
-        <v>0.04113372965831982</v>
+        <v>-0.02865849234564319</v>
       </c>
       <c r="H3">
-        <v>0.02600132108328829</v>
+        <v>-0.04781252267285788</v>
       </c>
       <c r="I3">
-        <v>-0.03554915030324866</v>
+        <v>-0.06087208880504971</v>
       </c>
       <c r="J3">
-        <v>-0.03554915030324866</v>
+        <v>-0.06087208880504971</v>
       </c>
       <c r="K3">
-        <v>157.3</v>
+        <v>-99.5</v>
       </c>
       <c r="L3">
-        <v>0.09445745511319283</v>
+        <v>-0.07219037945294929</v>
       </c>
       <c r="M3">
-        <v>0.499</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.004004815409309792</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.003172282263191354</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -761,82 +752,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>0.499</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>23</v>
+        <v>24.6</v>
       </c>
       <c r="V3">
-        <v>0.1845906902086678</v>
+        <v>0.1589147286821705</v>
       </c>
       <c r="W3">
-        <v>0.3197154471544716</v>
+        <v>-0.3055896805896806</v>
       </c>
       <c r="X3">
-        <v>0.2683463109506102</v>
+        <v>0.1616288447441349</v>
       </c>
       <c r="Y3">
-        <v>0.05136913620386135</v>
+        <v>-0.4672185253338154</v>
       </c>
       <c r="Z3">
-        <v>1.735229759299781</v>
+        <v>2.019783118405627</v>
       </c>
       <c r="AA3">
-        <v>-0.06168594352401792</v>
+        <v>-0.1229484173505276</v>
       </c>
       <c r="AB3">
-        <v>0.1261211761872993</v>
+        <v>0.07401100354284262</v>
       </c>
       <c r="AC3">
-        <v>-0.1878071197113172</v>
+        <v>-0.1969594208933702</v>
       </c>
       <c r="AD3">
-        <v>424.5</v>
+        <v>391.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>424.5</v>
+        <v>391.2</v>
       </c>
       <c r="AG3">
-        <v>401.5</v>
+        <v>366.6</v>
       </c>
       <c r="AH3">
-        <v>0.7730832270988891</v>
+        <v>0.7164835164835165</v>
       </c>
       <c r="AI3">
-        <v>0.5659245433942141</v>
+        <v>0.6342412451361868</v>
       </c>
       <c r="AJ3">
-        <v>0.7631628967876829</v>
+        <v>0.7031070195627157</v>
       </c>
       <c r="AK3">
-        <v>0.5521936459909228</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="AL3">
-        <v>23.9</v>
+        <v>25.5</v>
       </c>
       <c r="AM3">
-        <v>23.9</v>
+        <v>25.5</v>
       </c>
       <c r="AN3">
-        <v>-11.53532608695652</v>
+        <v>-6.596964586846543</v>
       </c>
       <c r="AO3">
-        <v>-2.476987447698745</v>
+        <v>-3.290196078431373</v>
       </c>
       <c r="AP3">
-        <v>-10.91032608695652</v>
+        <v>-6.182124789207419</v>
       </c>
       <c r="AQ3">
-        <v>-2.476987447698745</v>
+        <v>-3.290196078431373</v>
       </c>
     </row>
   </sheetData>
